--- a/LWL_WQ_Data.xlsx
+++ b/LWL_WQ_Data.xlsx
@@ -80,12 +80,6 @@
     <t xml:space="preserve">AnalysisDate</t>
   </si>
   <si>
-    <t xml:space="preserve">LWL19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LWL20</t>
-  </si>
-  <si>
     <t xml:space="preserve">LW-L1</t>
   </si>
   <si>
@@ -104,10 +98,16 @@
     <t xml:space="preserve">LW-R4</t>
   </si>
   <si>
-    <t xml:space="preserve">SC</t>
+    <t xml:space="preserve">LWL19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LWL20</t>
   </si>
   <si>
     <t xml:space="preserve">NC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC</t>
   </si>
   <si>
     <t xml:space="preserve">LWL19_Turb</t>
@@ -62110,19 +62110,33 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="F2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="I2" t="n">
         <v>26.9928699466056</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
       <c r="J2"/>
       <c r="K2" t="n">
-        <v>26.9928699466056</v>
-      </c>
-      <c r="L2"/>
+        <v>17.8166666666667</v>
+      </c>
+      <c r="L2" t="n">
+        <v>25.0983876811594</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -62132,22 +62146,34 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="D3" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="E3" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="F3" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="H3" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="I3" t="n">
         <v>26.4405339371981</v>
       </c>
-      <c r="D3" t="n">
+      <c r="J3" t="n">
         <v>29.4527173913044</v>
       </c>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
       <c r="K3" t="n">
-        <v>26.4405339371981</v>
+        <v>32.8310869565217</v>
       </c>
       <c r="L3" t="n">
-        <v>29.4527173913044</v>
+        <v>27.5580767080745</v>
       </c>
     </row>
     <row r="4">
@@ -62158,34 +62184,34 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="D4" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="F4" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="H4" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="I4" t="n">
         <v>27.0444918001526</v>
       </c>
-      <c r="D4" t="n">
+      <c r="J4" t="n">
         <v>26.565349976916</v>
       </c>
-      <c r="E4" t="n">
-        <v>29.38</v>
-      </c>
-      <c r="F4" t="n">
-        <v>28.64</v>
-      </c>
-      <c r="G4" t="n">
-        <v>30.94</v>
-      </c>
-      <c r="H4" t="n">
-        <v>28.38</v>
-      </c>
-      <c r="I4" t="n">
-        <v>30.03</v>
-      </c>
-      <c r="J4" t="n">
-        <v>29.22</v>
-      </c>
       <c r="K4" t="n">
+        <v>26.9082567982456</v>
+      </c>
+      <c r="L4" t="n">
         <v>27.4179701910409</v>
-      </c>
-      <c r="L4" t="n">
-        <v>26.9082567982456</v>
       </c>
     </row>
     <row r="5">
@@ -62196,22 +62222,34 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="D5" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="E5" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="H5" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="I5" t="n">
         <v>28.3205133758309</v>
       </c>
-      <c r="D5" t="n">
+      <c r="J5" t="n">
         <v>27.3196721491228</v>
       </c>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
       <c r="K5" t="n">
-        <v>28.3205133758309</v>
+        <v>27.2438077651515</v>
       </c>
       <c r="L5" t="n">
-        <v>27.3196721491228</v>
+        <v>28.1904433700358</v>
       </c>
     </row>
     <row r="6">
@@ -62222,34 +62260,34 @@
         <v>15</v>
       </c>
       <c r="C6" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="D6" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="E6" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="F6" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="G6" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="H6" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="I6" t="n">
         <v>30.8807425404945</v>
       </c>
-      <c r="D6" t="n">
+      <c r="J6" t="n">
         <v>31.341402136522</v>
       </c>
-      <c r="E6" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="F6" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="G6" t="n">
-        <v>34.41</v>
-      </c>
-      <c r="H6" t="n">
-        <v>32.56</v>
-      </c>
-      <c r="I6" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="J6" t="n">
-        <v>32.87</v>
-      </c>
       <c r="K6" t="n">
+        <v>31.4936918160437</v>
+      </c>
+      <c r="L6" t="n">
         <v>31.2256311594203</v>
-      </c>
-      <c r="L6" t="n">
-        <v>31.4936918160437</v>
       </c>
     </row>
     <row r="7">
@@ -62260,34 +62298,34 @@
         <v>15</v>
       </c>
       <c r="C7" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="E7" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="G7" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="H7" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="I7" t="n">
         <v>29.8794033116679</v>
       </c>
-      <c r="D7" t="n">
+      <c r="J7" t="n">
         <v>28.0214273455377</v>
       </c>
-      <c r="E7" t="n">
-        <v>27.69</v>
-      </c>
-      <c r="F7" t="n">
-        <v>27.06</v>
-      </c>
-      <c r="G7" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>27.31</v>
-      </c>
-      <c r="I7" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="J7" t="n">
-        <v>28.77</v>
-      </c>
       <c r="K7" t="n">
+        <v>27.9966872529644</v>
+      </c>
+      <c r="L7" t="n">
         <v>29.5290301328041</v>
-      </c>
-      <c r="L7" t="n">
-        <v>27.9966872529644</v>
       </c>
     </row>
     <row r="8">
@@ -62298,34 +62336,34 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="E8" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="G8" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="H8" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="I8" t="n">
         <v>35.3822680871866</v>
       </c>
-      <c r="D8" t="n">
+      <c r="J8" t="n">
         <v>28.9306028582931</v>
       </c>
-      <c r="E8" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="G8" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="I8" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="J8" t="n">
-        <v>32.54</v>
-      </c>
       <c r="K8" t="n">
+        <v>29.3681357832988</v>
+      </c>
+      <c r="L8" t="n">
         <v>34.9033726461599</v>
-      </c>
-      <c r="L8" t="n">
-        <v>29.3681357832988</v>
       </c>
     </row>
     <row r="9">
@@ -62336,34 +62374,34 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="E9" t="n">
+        <v>37.66</v>
+      </c>
+      <c r="F9" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="G9" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="H9" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="I9" t="n">
         <v>36.3751341273143</v>
       </c>
-      <c r="D9" t="n">
+      <c r="J9" t="n">
         <v>36.5481314175908</v>
       </c>
-      <c r="E9" t="n">
-        <v>35.33</v>
-      </c>
-      <c r="F9" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="G9" t="n">
-        <v>37.66</v>
-      </c>
-      <c r="H9" t="n">
-        <v>36.53</v>
-      </c>
-      <c r="I9" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="J9" t="n">
-        <v>35.11</v>
-      </c>
       <c r="K9" t="n">
+        <v>36.3874771333739</v>
+      </c>
+      <c r="L9" t="n">
         <v>36.4471612917715</v>
-      </c>
-      <c r="L9" t="n">
-        <v>36.3874771333739</v>
       </c>
     </row>
     <row r="10">
@@ -62374,34 +62412,34 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="E10" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="G10" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="H10" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="I10" t="n">
         <v>27.0421833762051</v>
       </c>
-      <c r="D10" t="n">
+      <c r="J10" t="n">
         <v>20.4941941150637</v>
       </c>
-      <c r="E10" t="n">
-        <v>36.13</v>
-      </c>
-      <c r="F10" t="n">
-        <v>35.66</v>
-      </c>
-      <c r="G10" t="n">
-        <v>37.07</v>
-      </c>
-      <c r="H10" t="n">
-        <v>36.62</v>
-      </c>
-      <c r="I10" t="n">
-        <v>36.53</v>
-      </c>
-      <c r="J10" t="n">
-        <v>35.86</v>
-      </c>
       <c r="K10" t="n">
+        <v>22.6926425748165</v>
+      </c>
+      <c r="L10" t="n">
         <v>28.427585751033</v>
-      </c>
-      <c r="L10" t="n">
-        <v>22.6926425748165</v>
       </c>
     </row>
     <row r="11">
@@ -62412,34 +62450,34 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="E11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="H11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I11" t="n">
         <v>30.9905774564871</v>
       </c>
-      <c r="D11" t="n">
+      <c r="J11" t="n">
         <v>26.4956474065599</v>
       </c>
-      <c r="E11" t="n">
-        <v>23.37</v>
-      </c>
-      <c r="F11" t="n">
-        <v>21.13</v>
-      </c>
-      <c r="G11" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="H11" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="I11" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="J11" t="n">
-        <v>25.2</v>
-      </c>
       <c r="K11" t="n">
+        <v>26.0507863965744</v>
+      </c>
+      <c r="L11" t="n">
         <v>30.2077714396934</v>
-      </c>
-      <c r="L11" t="n">
-        <v>26.0507863965744</v>
       </c>
     </row>
     <row r="12">
@@ -62450,34 +62488,34 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D12" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="E12" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="F12" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="G12" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="H12" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="I12" t="n">
         <v>29.0452784134249</v>
       </c>
-      <c r="D12" t="n">
+      <c r="J12" t="n">
         <v>26.7818039664378</v>
       </c>
-      <c r="E12" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="F12" t="n">
-        <v>20.31</v>
-      </c>
-      <c r="G12" t="n">
-        <v>32.69</v>
-      </c>
-      <c r="H12" t="n">
-        <v>31.95</v>
-      </c>
-      <c r="I12" t="n">
-        <v>32.83</v>
-      </c>
-      <c r="J12" t="n">
-        <v>29.67</v>
-      </c>
       <c r="K12" t="n">
+        <v>26.8451943346509</v>
+      </c>
+      <c r="L12" t="n">
         <v>29.5150131752306</v>
-      </c>
-      <c r="L12" t="n">
-        <v>26.8451943346509</v>
       </c>
     </row>
     <row r="13">
@@ -62488,34 +62526,34 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="D13" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="G13" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="H13" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="I13" t="n">
         <v>24.1451185185185</v>
       </c>
-      <c r="D13" t="n">
+      <c r="J13" t="n">
         <v>21.0521668679549</v>
       </c>
-      <c r="E13" t="n">
-        <v>19.46</v>
-      </c>
-      <c r="F13" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="G13" t="n">
-        <v>25.83</v>
-      </c>
-      <c r="H13" t="n">
-        <v>22.89</v>
-      </c>
-      <c r="I13" t="n">
-        <v>23.69</v>
-      </c>
-      <c r="J13" t="n">
-        <v>21.52</v>
-      </c>
       <c r="K13" t="n">
+        <v>20.7004287439614</v>
+      </c>
+      <c r="L13" t="n">
         <v>24.1439111111111</v>
-      </c>
-      <c r="L13" t="n">
-        <v>20.7004287439614</v>
       </c>
     </row>
     <row r="14">
@@ -62526,34 +62564,34 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="E14" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="F14" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="G14" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="H14" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="I14" t="n">
         <v>15.9785621843434</v>
       </c>
-      <c r="D14" t="n">
+      <c r="J14" t="n">
         <v>20.4607529918753</v>
       </c>
-      <c r="E14" t="n">
-        <v>21.13</v>
-      </c>
-      <c r="F14" t="n">
-        <v>17.18</v>
-      </c>
-      <c r="G14" t="n">
-        <v>24.61</v>
-      </c>
-      <c r="H14" t="n">
-        <v>22.17</v>
-      </c>
-      <c r="I14" t="n">
-        <v>22.45</v>
-      </c>
-      <c r="J14" t="n">
-        <v>25.56</v>
-      </c>
       <c r="K14" t="n">
+        <v>20.6266023935002</v>
+      </c>
+      <c r="L14" t="n">
         <v>17.0993155236576</v>
-      </c>
-      <c r="L14" t="n">
-        <v>20.6266023935002</v>
       </c>
     </row>
     <row r="15">
@@ -62564,34 +62602,34 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="E15" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="F15" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="I15" t="n">
         <v>29.4527537464978</v>
       </c>
-      <c r="D15" t="n">
+      <c r="J15" t="n">
         <v>31.2036416666667</v>
       </c>
-      <c r="E15" t="n">
-        <v>27.12</v>
-      </c>
-      <c r="F15" t="n">
-        <v>24.53</v>
-      </c>
-      <c r="G15" t="n">
-        <v>28.38</v>
-      </c>
-      <c r="H15" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="I15" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>28.05</v>
-      </c>
       <c r="K15" t="n">
+        <v>30.1335705128205</v>
+      </c>
+      <c r="L15" t="n">
         <v>28.8012663128403</v>
-      </c>
-      <c r="L15" t="n">
-        <v>30.1335705128205</v>
       </c>
     </row>
     <row r="16">
@@ -62602,34 +62640,34 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="D16" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="E16" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>33.71</v>
+      </c>
+      <c r="G16" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="H16" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="I16" t="n">
         <v>28.5572149122807</v>
       </c>
-      <c r="D16" t="n">
+      <c r="J16" t="n">
         <v>31.3054995868413</v>
       </c>
-      <c r="E16" t="n">
-        <v>35.07</v>
-      </c>
-      <c r="F16" t="n">
-        <v>34.24</v>
-      </c>
-      <c r="G16" t="n">
-        <v>32.48</v>
-      </c>
-      <c r="H16" t="n">
-        <v>33.71</v>
-      </c>
-      <c r="I16" t="n">
-        <v>33.25</v>
-      </c>
-      <c r="J16" t="n">
-        <v>35.83</v>
-      </c>
       <c r="K16" t="n">
+        <v>31.8962101783927</v>
+      </c>
+      <c r="L16" t="n">
         <v>29.1830492424243</v>
-      </c>
-      <c r="L16" t="n">
-        <v>31.8962101783927</v>
       </c>
     </row>
     <row r="17">
@@ -62640,34 +62678,34 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="D17" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="G17" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="H17" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="I17" t="n">
         <v>26.6640964237749</v>
       </c>
-      <c r="D17" t="n">
+      <c r="J17" t="n">
         <v>27.4340652014652</v>
       </c>
-      <c r="E17" t="n">
-        <v>25.49</v>
-      </c>
-      <c r="F17" t="n">
-        <v>23.07</v>
-      </c>
-      <c r="G17" t="n">
-        <v>29.24</v>
-      </c>
-      <c r="H17" t="n">
-        <v>23.61</v>
-      </c>
-      <c r="I17" t="n">
-        <v>26.44</v>
-      </c>
-      <c r="J17" t="n">
-        <v>27.49</v>
-      </c>
       <c r="K17" t="n">
+        <v>27.1622306099697</v>
+      </c>
+      <c r="L17" t="n">
         <v>26.6434408569713</v>
-      </c>
-      <c r="L17" t="n">
-        <v>27.1622306099697</v>
       </c>
     </row>
     <row r="18">
@@ -62678,34 +62716,34 @@
         <v>15</v>
       </c>
       <c r="C18" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="D18" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="E18" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="F18" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="H18" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="I18" t="n">
         <v>28.9130357142857</v>
       </c>
-      <c r="D18" t="n">
+      <c r="J18" t="n">
         <v>26.8783941511387</v>
       </c>
-      <c r="E18" t="n">
-        <v>26.07</v>
-      </c>
-      <c r="F18" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="G18" t="n">
-        <v>30.74</v>
-      </c>
-      <c r="H18" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>26.66</v>
-      </c>
-      <c r="J18" t="n">
-        <v>29.48</v>
-      </c>
       <c r="K18" t="n">
+        <v>26.8250011687705</v>
+      </c>
+      <c r="L18" t="n">
         <v>28.8117741935484</v>
-      </c>
-      <c r="L18" t="n">
-        <v>26.8250011687705</v>
       </c>
     </row>
     <row r="19">
@@ -62716,34 +62754,34 @@
         <v>15</v>
       </c>
       <c r="C19" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="F19" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="G19" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="H19" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="I19" t="n">
         <v>30.6225946704067</v>
       </c>
-      <c r="D19" t="n">
+      <c r="J19" t="n">
         <v>28.3734467040673</v>
       </c>
-      <c r="E19" t="n">
-        <v>26.78</v>
-      </c>
-      <c r="F19" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G19" t="n">
-        <v>34.67</v>
-      </c>
-      <c r="H19" t="n">
-        <v>28.29</v>
-      </c>
-      <c r="I19" t="n">
-        <v>32.09</v>
-      </c>
-      <c r="J19" t="n">
-        <v>26.27</v>
-      </c>
       <c r="K19" t="n">
+        <v>28.177260230179</v>
+      </c>
+      <c r="L19" t="n">
         <v>30.716189258312</v>
-      </c>
-      <c r="L19" t="n">
-        <v>28.177260230179</v>
       </c>
     </row>
     <row r="20">
@@ -62754,34 +62792,34 @@
         <v>15</v>
       </c>
       <c r="C20" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="D20" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="E20" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="F20" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="G20" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="H20" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="I20" t="n">
         <v>34.0686164787976</v>
       </c>
-      <c r="D20" t="n">
+      <c r="J20" t="n">
         <v>35.7144058435526</v>
       </c>
-      <c r="E20" t="n">
-        <v>35.26</v>
-      </c>
-      <c r="F20" t="n">
-        <v>35.32</v>
-      </c>
-      <c r="G20" t="n">
-        <v>35.92</v>
-      </c>
-      <c r="H20" t="n">
-        <v>35.65</v>
-      </c>
-      <c r="I20" t="n">
-        <v>35.33</v>
-      </c>
-      <c r="J20" t="n">
-        <v>34.72</v>
-      </c>
       <c r="K20" t="n">
+        <v>35.658550766866</v>
+      </c>
+      <c r="L20" t="n">
         <v>34.2250881642512</v>
-      </c>
-      <c r="L20" t="n">
-        <v>35.658550766866</v>
       </c>
     </row>
     <row r="21">
@@ -62792,34 +62830,34 @@
         <v>15</v>
       </c>
       <c r="C21" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="D21" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="E21" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="G21" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="H21" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="I21" t="n">
         <v>34.3335752688172</v>
       </c>
-      <c r="D21" t="n">
+      <c r="J21" t="n">
         <v>34.468069068323</v>
       </c>
-      <c r="E21" t="n">
-        <v>37.94</v>
-      </c>
-      <c r="F21" t="n">
-        <v>37.85</v>
-      </c>
-      <c r="G21" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="H21" t="n">
-        <v>37.83</v>
-      </c>
-      <c r="I21" t="n">
-        <v>37.82</v>
-      </c>
-      <c r="J21" t="n">
-        <v>37.72</v>
-      </c>
       <c r="K21" t="n">
+        <v>34.8289902395741</v>
+      </c>
+      <c r="L21" t="n">
         <v>34.6409068627451</v>
-      </c>
-      <c r="L21" t="n">
-        <v>34.8289902395741</v>
       </c>
     </row>
     <row r="22">
@@ -62830,34 +62868,34 @@
         <v>15</v>
       </c>
       <c r="C22" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="D22" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>35.72</v>
+      </c>
+      <c r="F22" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="G22" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="H22" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="I22" t="n">
         <v>31.1572844202899</v>
       </c>
-      <c r="D22" t="n">
+      <c r="J22" t="n">
         <v>33.8111998737374</v>
       </c>
-      <c r="E22" t="n">
-        <v>32.74</v>
-      </c>
-      <c r="F22" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="G22" t="n">
-        <v>35.72</v>
-      </c>
-      <c r="H22" t="n">
-        <v>33.83</v>
-      </c>
-      <c r="I22" t="n">
-        <v>34.47</v>
-      </c>
-      <c r="J22" t="n">
-        <v>33.03</v>
-      </c>
       <c r="K22" t="n">
+        <v>33.7274544306703</v>
+      </c>
+      <c r="L22" t="n">
         <v>31.4769252305665</v>
-      </c>
-      <c r="L22" t="n">
-        <v>33.7274544306703</v>
       </c>
     </row>
     <row r="23">
@@ -62868,34 +62906,34 @@
         <v>15</v>
       </c>
       <c r="C23" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="D23" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="E23" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="F23" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="G23" t="n">
+        <v>32</v>
+      </c>
+      <c r="H23" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="I23" t="n">
         <v>32.9229493922394</v>
       </c>
-      <c r="D23" t="n">
+      <c r="J23" t="n">
         <v>29.4290784244974</v>
       </c>
-      <c r="E23" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="F23" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="G23" t="n">
-        <v>34.18</v>
-      </c>
-      <c r="H23" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="I23" t="n">
-        <v>32</v>
-      </c>
-      <c r="J23" t="n">
-        <v>33.07</v>
-      </c>
       <c r="K23" t="n">
+        <v>29.6223950341006</v>
+      </c>
+      <c r="L23" t="n">
         <v>32.894159739983</v>
-      </c>
-      <c r="L23" t="n">
-        <v>29.6223950341006</v>
       </c>
     </row>
     <row r="24">
@@ -62906,34 +62944,34 @@
         <v>15</v>
       </c>
       <c r="C24" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="D24" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="E24" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="F24" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="G24" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="H24" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="I24" t="n">
         <v>32.7163218793829</v>
       </c>
-      <c r="D24" t="n">
+      <c r="J24" t="n">
         <v>29.0567209188661</v>
       </c>
-      <c r="E24" t="n">
-        <v>32.21</v>
-      </c>
-      <c r="F24" t="n">
-        <v>32.53</v>
-      </c>
-      <c r="G24" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="H24" t="n">
-        <v>33.69</v>
-      </c>
-      <c r="I24" t="n">
-        <v>34.02</v>
-      </c>
-      <c r="J24" t="n">
-        <v>31.61</v>
-      </c>
       <c r="K24" t="n">
+        <v>29.3267161319073</v>
+      </c>
+      <c r="L24" t="n">
         <v>32.849881713555</v>
-      </c>
-      <c r="L24" t="n">
-        <v>29.3267161319073</v>
       </c>
     </row>
     <row r="25">
@@ -62944,34 +62982,34 @@
         <v>15</v>
       </c>
       <c r="C25" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="E25" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="F25" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="G25" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="H25" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="I25" t="n">
         <v>16.1646957246377</v>
       </c>
-      <c r="D25" t="n">
+      <c r="J25" t="n">
         <v>18.9404997076023</v>
       </c>
-      <c r="E25" t="n">
-        <v>26.63</v>
-      </c>
-      <c r="F25" t="n">
-        <v>25.29</v>
-      </c>
-      <c r="G25" t="n">
-        <v>26.43</v>
-      </c>
-      <c r="H25" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="I25" t="n">
-        <v>25.83</v>
-      </c>
-      <c r="J25" t="n">
-        <v>27.93</v>
-      </c>
       <c r="K25" t="n">
+        <v>19.6383330675173</v>
+      </c>
+      <c r="L25" t="n">
         <v>17.0651779314888</v>
-      </c>
-      <c r="L25" t="n">
-        <v>19.6383330675173</v>
       </c>
     </row>
     <row r="26">
@@ -62982,34 +63020,34 @@
         <v>15</v>
       </c>
       <c r="C26" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="D26" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="E26" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="F26" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="G26" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="H26" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="I26" t="n">
         <v>23.0033773420362</v>
       </c>
-      <c r="D26" t="n">
+      <c r="J26" t="n">
         <v>24.3182632340777</v>
       </c>
-      <c r="E26" t="n">
-        <v>23.64</v>
-      </c>
-      <c r="F26" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="G26" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="H26" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="I26" t="n">
-        <v>21.12</v>
-      </c>
-      <c r="J26" t="n">
-        <v>26.45</v>
-      </c>
       <c r="K26" t="n">
+        <v>24.234887066365</v>
+      </c>
+      <c r="L26" t="n">
         <v>22.9124911059742</v>
-      </c>
-      <c r="L26" t="n">
-        <v>24.234887066365</v>
       </c>
     </row>
     <row r="27">
@@ -63020,34 +63058,34 @@
         <v>15</v>
       </c>
       <c r="C27" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="D27" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="E27" t="n">
+        <v>26.23</v>
+      </c>
+      <c r="F27" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="G27" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="H27" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="I27" t="n">
         <v>30.8256302222222</v>
       </c>
-      <c r="D27" t="n">
+      <c r="J27" t="n">
         <v>30.5303944444444</v>
       </c>
-      <c r="E27" t="n">
-        <v>27.36</v>
-      </c>
-      <c r="F27" t="n">
-        <v>26.09</v>
-      </c>
-      <c r="G27" t="n">
-        <v>26.23</v>
-      </c>
-      <c r="H27" t="n">
-        <v>25.21</v>
-      </c>
-      <c r="I27" t="n">
-        <v>25.39</v>
-      </c>
-      <c r="J27" t="n">
-        <v>29.24</v>
-      </c>
       <c r="K27" t="n">
+        <v>30.2606616161616</v>
+      </c>
+      <c r="L27" t="n">
         <v>30.351482020202</v>
-      </c>
-      <c r="L27" t="n">
-        <v>30.2606616161616</v>
       </c>
     </row>
     <row r="28">
@@ -63058,34 +63096,34 @@
         <v>15</v>
       </c>
       <c r="C28" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="D28" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="E28" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="F28" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="G28" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="H28" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="I28" t="n">
         <v>32.6624180691912</v>
       </c>
-      <c r="D28" t="n">
+      <c r="J28" t="n">
         <v>32.3283667367929</v>
       </c>
-      <c r="E28" t="n">
-        <v>30.97</v>
-      </c>
-      <c r="F28" t="n">
-        <v>30.78</v>
-      </c>
-      <c r="G28" t="n">
-        <v>32.85</v>
-      </c>
-      <c r="H28" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="I28" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="J28" t="n">
-        <v>32.66</v>
-      </c>
       <c r="K28" t="n">
+        <v>32.2526284953112</v>
+      </c>
+      <c r="L28" t="n">
         <v>32.6407341219096</v>
-      </c>
-      <c r="L28" t="n">
-        <v>32.2526284953112</v>
       </c>
     </row>
     <row r="29">
@@ -63096,34 +63134,34 @@
         <v>15</v>
       </c>
       <c r="C29" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="D29" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="E29" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="F29" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="G29" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="H29" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="I29" t="n">
         <v>34.0944904160823</v>
       </c>
-      <c r="D29" t="n">
+      <c r="J29" t="n">
         <v>34.4286214352501</v>
       </c>
-      <c r="E29" t="n">
-        <v>34.35</v>
-      </c>
-      <c r="F29" t="n">
-        <v>34.05</v>
-      </c>
-      <c r="G29" t="n">
-        <v>34.08</v>
-      </c>
-      <c r="H29" t="n">
-        <v>33.79</v>
-      </c>
-      <c r="I29" t="n">
-        <v>33.73</v>
-      </c>
-      <c r="J29" t="n">
-        <v>35.36</v>
-      </c>
       <c r="K29" t="n">
+        <v>34.442566602728</v>
+      </c>
+      <c r="L29" t="n">
         <v>34.0743883205456</v>
-      </c>
-      <c r="L29" t="n">
-        <v>34.442566602728</v>
       </c>
     </row>
     <row r="30">
@@ -63134,34 +63172,34 @@
         <v>15</v>
       </c>
       <c r="C30" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="D30" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="F30" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="G30" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="H30" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="I30" t="n">
         <v>34.9904878364389</v>
       </c>
-      <c r="D30" t="n">
+      <c r="J30" t="n">
         <v>35.1304166666667</v>
       </c>
-      <c r="E30" t="n">
-        <v>35.68</v>
-      </c>
-      <c r="F30" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="G30" t="n">
-        <v>35.02</v>
-      </c>
-      <c r="H30" t="n">
-        <v>35.33</v>
-      </c>
-      <c r="I30" t="n">
-        <v>35.37</v>
-      </c>
-      <c r="J30" t="n">
-        <v>36.15</v>
-      </c>
       <c r="K30" t="n">
+        <v>35.1994086021505</v>
+      </c>
+      <c r="L30" t="n">
         <v>35.0146341748481</v>
-      </c>
-      <c r="L30" t="n">
-        <v>35.1994086021505</v>
       </c>
     </row>
     <row r="31">
@@ -63172,34 +63210,34 @@
         <v>15</v>
       </c>
       <c r="C31" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="D31" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="F31" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="G31" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="H31" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="I31" t="n">
         <v>33.6268084066471</v>
       </c>
-      <c r="D31" t="n">
+      <c r="J31" t="n">
         <v>34.1694745845552</v>
       </c>
-      <c r="E31" t="n">
-        <v>35.21</v>
-      </c>
-      <c r="F31" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="G31" t="n">
-        <v>36.48</v>
-      </c>
-      <c r="H31" t="n">
-        <v>36.33</v>
-      </c>
-      <c r="I31" t="n">
-        <v>36.22</v>
-      </c>
-      <c r="J31" t="n">
-        <v>34.67</v>
-      </c>
       <c r="K31" t="n">
+        <v>34.2509915329768</v>
+      </c>
+      <c r="L31" t="n">
         <v>33.8665017825312</v>
-      </c>
-      <c r="L31" t="n">
-        <v>34.2509915329768</v>
       </c>
     </row>
     <row r="32">
@@ -63210,34 +63248,34 @@
         <v>15</v>
       </c>
       <c r="C32" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="E32" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="H32" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I32" t="n">
         <v>25.8766408730159</v>
       </c>
-      <c r="D32" t="n">
+      <c r="J32" t="n">
         <v>25.9598826086957</v>
       </c>
-      <c r="E32" t="n">
-        <v>23.79</v>
-      </c>
-      <c r="F32" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="G32" t="n">
-        <v>21.98</v>
-      </c>
-      <c r="H32" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="I32" t="n">
-        <v>20.76</v>
-      </c>
-      <c r="J32" t="n">
-        <v>23.7</v>
-      </c>
       <c r="K32" t="n">
+        <v>25.5195902503294</v>
+      </c>
+      <c r="L32" t="n">
         <v>25.4814917027417</v>
-      </c>
-      <c r="L32" t="n">
-        <v>25.5195902503294</v>
       </c>
     </row>
     <row r="33">
@@ -63248,34 +63286,102 @@
         <v>15</v>
       </c>
       <c r="C33" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="D33" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="E33" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="F33" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="G33" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="H33" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="I33" t="n">
         <v>30.7267730247779</v>
       </c>
-      <c r="D33" t="n">
+      <c r="J33" t="n">
         <v>30.2123200093502</v>
       </c>
-      <c r="E33" t="n">
-        <v>30.31</v>
-      </c>
-      <c r="F33" t="n">
-        <v>28.24</v>
-      </c>
-      <c r="G33" t="n">
-        <v>28.01</v>
-      </c>
-      <c r="H33" t="n">
-        <v>26.85</v>
-      </c>
-      <c r="I33" t="n">
-        <v>24.91</v>
-      </c>
-      <c r="J33" t="n">
-        <v>32.6</v>
-      </c>
       <c r="K33" t="n">
+        <v>30.2274094202899</v>
+      </c>
+      <c r="L33" t="n">
         <v>30.3617636402387</v>
       </c>
-      <c r="L33" t="n">
-        <v>30.2274094202899</v>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="D34" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="E34" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="F34" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="G34" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="H34" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34" t="n">
+        <v>31.7733333333333</v>
+      </c>
+      <c r="L34" t="n">
+        <v>33.4066666666667</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="D35" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="E35" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="F35" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="H35" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35" t="n">
+        <v>33.9666666666667</v>
+      </c>
+      <c r="L35" t="n">
+        <v>34.4766666666667</v>
       </c>
     </row>
   </sheetData>
@@ -79022,19 +79128,33 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="I2" t="n">
         <v>15.1259631006865</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
       <c r="J2"/>
       <c r="K2" t="n">
-        <v>15.1259631006865</v>
-      </c>
-      <c r="L2"/>
+        <v>4.34</v>
+      </c>
+      <c r="L2" t="n">
+        <v>13.6946954051383</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -79044,22 +79164,34 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I3" t="n">
         <v>162.698979367955</v>
       </c>
-      <c r="D3" t="n">
+      <c r="J3" t="n">
         <v>3.36081317934782</v>
       </c>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
       <c r="K3" t="n">
-        <v>162.698979367955</v>
+        <v>3.50432527173913</v>
       </c>
       <c r="L3" t="n">
-        <v>3.36081317934782</v>
+        <v>140.54817279158</v>
       </c>
     </row>
     <row r="4">
@@ -79070,34 +79202,34 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I4" t="n">
         <v>27.4412134820748</v>
       </c>
-      <c r="D4" t="n">
+      <c r="J4" t="n">
         <v>33.1912875807941</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.74</v>
-      </c>
       <c r="K4" t="n">
+        <v>29.0302029106858</v>
+      </c>
+      <c r="L4" t="n">
         <v>24.1855934617918</v>
-      </c>
-      <c r="L4" t="n">
-        <v>29.0302029106858</v>
       </c>
     </row>
     <row r="5">
@@ -79108,22 +79240,34 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
         <v>632.856878398442</v>
       </c>
-      <c r="D5" t="n">
+      <c r="J5" t="n">
         <v>120.102553179825</v>
       </c>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
       <c r="K5" t="n">
-        <v>632.856878398442</v>
+        <v>104.080386837121</v>
       </c>
       <c r="L5" t="n">
-        <v>120.102553179825</v>
+        <v>546.818213162291</v>
       </c>
     </row>
     <row r="6">
@@ -79134,34 +79278,34 @@
         <v>15</v>
       </c>
       <c r="C6" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="I6" t="n">
         <v>13.9020066922421</v>
       </c>
-      <c r="D6" t="n">
+      <c r="J6" t="n">
         <v>561.614408904294</v>
       </c>
-      <c r="E6" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="F6" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="G6" t="n">
-        <v>19.93</v>
-      </c>
-      <c r="H6" t="n">
-        <v>16.04</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>8.26</v>
-      </c>
       <c r="K6" t="n">
+        <v>479.02374756865</v>
+      </c>
+      <c r="L6" t="n">
         <v>14.1402056884058</v>
-      </c>
-      <c r="L6" t="n">
-        <v>479.02374756865</v>
       </c>
     </row>
     <row r="7">
@@ -79172,34 +79316,34 @@
         <v>15</v>
       </c>
       <c r="C7" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="I7" t="n">
         <v>132.894742588933</v>
       </c>
-      <c r="D7" t="n">
+      <c r="J7" t="n">
         <v>36.7965486660079</v>
       </c>
-      <c r="E7" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="F7" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="H7" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11.37</v>
-      </c>
       <c r="K7" t="n">
+        <v>31.8683341955359</v>
+      </c>
+      <c r="L7" t="n">
         <v>115.595914054078</v>
-      </c>
-      <c r="L7" t="n">
-        <v>31.8683341955359</v>
       </c>
     </row>
     <row r="8">
@@ -79210,34 +79354,34 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I8" t="n">
         <v>74.722145100069</v>
       </c>
-      <c r="D8" t="n">
+      <c r="J8" t="n">
         <v>327.651390096618</v>
       </c>
-      <c r="E8" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>33.65</v>
-      </c>
-      <c r="I8" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.42</v>
-      </c>
       <c r="K8" t="n">
+        <v>281.498810559006</v>
+      </c>
+      <c r="L8" t="n">
         <v>66.631838657202</v>
-      </c>
-      <c r="L8" t="n">
-        <v>281.498810559006</v>
       </c>
     </row>
     <row r="9">
@@ -79248,34 +79392,34 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="I9" t="n">
         <v>36.6213613636364</v>
       </c>
-      <c r="D9" t="n">
+      <c r="J9" t="n">
         <v>65.9095286774629</v>
       </c>
-      <c r="E9" t="n">
-        <v>8.03</v>
-      </c>
-      <c r="F9" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="H9" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6.06</v>
-      </c>
       <c r="K9" t="n">
+        <v>58.1823202214453</v>
+      </c>
+      <c r="L9" t="n">
         <v>26.8796008522727</v>
-      </c>
-      <c r="L9" t="n">
-        <v>58.1823202214453</v>
       </c>
     </row>
     <row r="10">
@@ -79286,34 +79430,34 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="D10" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="F10" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="I10" t="n">
         <v>105.50306868896</v>
       </c>
-      <c r="D10" t="n">
+      <c r="J10" t="n">
         <v>241.057104139218</v>
       </c>
-      <c r="E10" t="n">
-        <v>12.46</v>
-      </c>
-      <c r="F10" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="G10" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="H10" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="J10" t="n">
-        <v>9.42</v>
-      </c>
       <c r="K10" t="n">
+        <v>208.908946405044</v>
+      </c>
+      <c r="L10" t="n">
         <v>92.4540588762515</v>
-      </c>
-      <c r="L10" t="n">
-        <v>208.908946405044</v>
       </c>
     </row>
     <row r="11">
@@ -79324,34 +79468,34 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.47</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
         <v>178.669174667152</v>
       </c>
-      <c r="D11" t="n">
+      <c r="J11" t="n">
         <v>159.45055682685</v>
       </c>
-      <c r="E11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="G11" t="n">
-        <v>8.47</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="n">
+        <v>137.938662714098</v>
+      </c>
+      <c r="L11" t="n">
         <v>155.068378121631</v>
-      </c>
-      <c r="L11" t="n">
-        <v>137.938662714098</v>
       </c>
     </row>
     <row r="12">
@@ -79362,34 +79506,34 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="F12" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="I12" t="n">
         <v>46.2367775553013</v>
       </c>
-      <c r="D12" t="n">
+      <c r="J12" t="n">
         <v>29.4666162280702</v>
       </c>
-      <c r="E12" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="F12" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="H12" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.68</v>
-      </c>
       <c r="K12" t="n">
+        <v>26.1561685606061</v>
+      </c>
+      <c r="L12" t="n">
         <v>41.5213078886693</v>
-      </c>
-      <c r="L12" t="n">
-        <v>26.1561685606061</v>
       </c>
     </row>
     <row r="13">
@@ -79400,34 +79544,34 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="I13" t="n">
         <v>84.8775817592592</v>
       </c>
-      <c r="D13" t="n">
+      <c r="J13" t="n">
         <v>20.1560309983897</v>
       </c>
-      <c r="E13" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="F13" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="H13" t="n">
-        <v>11.23</v>
-      </c>
-      <c r="I13" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.88</v>
-      </c>
       <c r="K13" t="n">
+        <v>18.0737408557626</v>
+      </c>
+      <c r="L13" t="n">
         <v>73.8607843650793</v>
-      </c>
-      <c r="L13" t="n">
-        <v>18.0737408557626</v>
       </c>
     </row>
     <row r="14">
@@ -79438,34 +79582,34 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I14" t="n">
         <v>227.341679811508</v>
       </c>
-      <c r="D14" t="n">
+      <c r="J14" t="n">
         <v>28.6123281845919</v>
       </c>
-      <c r="E14" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11.23</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.97</v>
-      </c>
       <c r="K14" t="n">
+        <v>25.273828886693</v>
+      </c>
+      <c r="L14" t="n">
         <v>192.456151420217</v>
-      </c>
-      <c r="L14" t="n">
-        <v>25.273828886693</v>
       </c>
     </row>
     <row r="15">
@@ -79476,34 +79620,34 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I15" t="n">
         <v>49.4776989734299</v>
       </c>
-      <c r="D15" t="n">
+      <c r="J15" t="n">
         <v>16.4553171296296</v>
       </c>
-      <c r="E15" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="F15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="H15" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.64</v>
-      </c>
       <c r="K15" t="n">
+        <v>14.740748015873</v>
+      </c>
+      <c r="L15" t="n">
         <v>43.0885038819876</v>
-      </c>
-      <c r="L15" t="n">
-        <v>14.740748015873</v>
       </c>
     </row>
     <row r="16">
@@ -79514,34 +79658,34 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I16" t="n">
         <v>107.398166666667</v>
       </c>
-      <c r="D16" t="n">
+      <c r="J16" t="n">
         <v>2.46898464912281</v>
       </c>
-      <c r="E16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="K16" t="n">
+        <v>2.37412310606061</v>
+      </c>
+      <c r="L16" t="n">
         <v>93.137053030303</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2.37412310606061</v>
       </c>
     </row>
     <row r="17">
@@ -79552,34 +79696,34 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I17" t="n">
         <v>149.547125541884</v>
       </c>
-      <c r="D17" t="n">
+      <c r="J17" t="n">
         <v>7.20641635098236</v>
       </c>
-      <c r="E17" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="H17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I17" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.34</v>
-      </c>
       <c r="K17" t="n">
+        <v>6.94144317051996</v>
+      </c>
+      <c r="L17" t="n">
         <v>136.849143876424</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6.94144317051996</v>
       </c>
     </row>
     <row r="18">
@@ -79590,34 +79734,34 @@
         <v>15</v>
       </c>
       <c r="C18" t="n">
+        <v>8.28</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8.95</v>
+      </c>
+      <c r="E18" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F18" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="I18" t="n">
         <v>56.2332340779691</v>
       </c>
-      <c r="D18" t="n">
+      <c r="J18" t="n">
         <v>232.593985183747</v>
       </c>
-      <c r="E18" t="n">
-        <v>8.28</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8.95</v>
-      </c>
-      <c r="G18" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="H18" t="n">
-        <v>24.08</v>
-      </c>
-      <c r="I18" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="J18" t="n">
-        <v>5.26</v>
-      </c>
       <c r="K18" t="n">
+        <v>210.810373714352</v>
+      </c>
+      <c r="L18" t="n">
         <v>52.1971146510689</v>
-      </c>
-      <c r="L18" t="n">
-        <v>210.810373714352</v>
       </c>
     </row>
     <row r="19">
@@ -79628,34 +79772,34 @@
         <v>15</v>
       </c>
       <c r="C19" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="D19" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I19" t="n">
         <v>187.522663394109</v>
       </c>
-      <c r="D19" t="n">
+      <c r="J19" t="n">
         <v>95.1640113370734</v>
       </c>
-      <c r="E19" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="F19" t="n">
-        <v>20.08</v>
-      </c>
-      <c r="G19" t="n">
-        <v>25.99</v>
-      </c>
-      <c r="H19" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="I19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.63</v>
-      </c>
       <c r="K19" t="n">
+        <v>87.6783632779199</v>
+      </c>
+      <c r="L19" t="n">
         <v>172.325957800511</v>
-      </c>
-      <c r="L19" t="n">
-        <v>87.6783632779199</v>
       </c>
     </row>
     <row r="20">
@@ -79666,34 +79810,34 @@
         <v>15</v>
       </c>
       <c r="C20" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="F20" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="I20" t="n">
         <v>267.890156648002</v>
       </c>
-      <c r="D20" t="n">
+      <c r="J20" t="n">
         <v>93.7145361111111</v>
       </c>
-      <c r="E20" t="n">
-        <v>11.23</v>
-      </c>
-      <c r="F20" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="H20" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="J20" t="n">
-        <v>4.55</v>
-      </c>
       <c r="K20" t="n">
+        <v>86.0326085858586</v>
+      </c>
+      <c r="L20" t="n">
         <v>244.213172710305</v>
-      </c>
-      <c r="L20" t="n">
-        <v>86.0326085858586</v>
       </c>
     </row>
     <row r="21">
@@ -79704,34 +79848,34 @@
         <v>15</v>
       </c>
       <c r="C21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8.87</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9.62</v>
+      </c>
+      <c r="I21" t="n">
         <v>19.8904731182796</v>
       </c>
-      <c r="D21" t="n">
+      <c r="J21" t="n">
         <v>14.7939509101449</v>
       </c>
-      <c r="E21" t="n">
-        <v>19</v>
-      </c>
-      <c r="F21" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="G21" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="H21" t="n">
-        <v>8.87</v>
-      </c>
-      <c r="I21" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="J21" t="n">
-        <v>9.62</v>
-      </c>
       <c r="K21" t="n">
+        <v>14.976741884058</v>
+      </c>
+      <c r="L21" t="n">
         <v>18.8783725490196</v>
-      </c>
-      <c r="L21" t="n">
-        <v>14.976741884058</v>
       </c>
     </row>
     <row r="22">
@@ -79742,34 +79886,34 @@
         <v>15</v>
       </c>
       <c r="C22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8.46</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I22" t="n">
         <v>326.664617753623</v>
       </c>
-      <c r="D22" t="n">
+      <c r="J22" t="n">
         <v>117.63835444847</v>
       </c>
-      <c r="E22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F22" t="n">
-        <v>8.46</v>
-      </c>
-      <c r="G22" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="H22" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="I22" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.28</v>
-      </c>
       <c r="K22" t="n">
+        <v>107.463352528912</v>
+      </c>
+      <c r="L22" t="n">
         <v>298.026622200263</v>
-      </c>
-      <c r="L22" t="n">
-        <v>107.463352528912</v>
       </c>
     </row>
     <row r="23">
@@ -79780,34 +79924,34 @@
         <v>15</v>
       </c>
       <c r="C23" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I23" t="n">
         <v>224.255307795699</v>
       </c>
-      <c r="D23" t="n">
+      <c r="J23" t="n">
         <v>7.71935268817204</v>
       </c>
-      <c r="E23" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="F23" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="G23" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="H23" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.81</v>
-      </c>
       <c r="K23" t="n">
+        <v>7.58029215686275</v>
+      </c>
+      <c r="L23" t="n">
         <v>205.367780637255</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7.58029215686275</v>
       </c>
     </row>
     <row r="24">
@@ -79818,34 +79962,34 @@
         <v>15</v>
       </c>
       <c r="C24" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9.39</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I24" t="n">
         <v>156.641700327256</v>
       </c>
-      <c r="D24" t="n">
+      <c r="J24" t="n">
         <v>0.418677908113392</v>
       </c>
-      <c r="E24" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="F24" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="G24" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="H24" t="n">
-        <v>9.39</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.42</v>
-      </c>
       <c r="K24" t="n">
+        <v>0.746735739750445</v>
+      </c>
+      <c r="L24" t="n">
         <v>143.522138533674</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.746735739750445</v>
       </c>
     </row>
     <row r="25">
@@ -79856,34 +80000,34 @@
         <v>15</v>
       </c>
       <c r="C25" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="I25" t="n">
         <v>687.906701193236</v>
       </c>
-      <c r="D25" t="n">
+      <c r="J25" t="n">
         <v>176.142542292347</v>
       </c>
-      <c r="E25" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="F25" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="G25" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="H25" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="I25" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5.28</v>
-      </c>
       <c r="K25" t="n">
+        <v>158.790210331069</v>
+      </c>
+      <c r="L25" t="n">
         <v>626.13700108476</v>
-      </c>
-      <c r="L25" t="n">
-        <v>158.790210331069</v>
       </c>
     </row>
     <row r="26">
@@ -79894,34 +80038,34 @@
         <v>15</v>
       </c>
       <c r="C26" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="D26" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="F26" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="I26" t="n">
         <v>44.398424088359</v>
       </c>
-      <c r="D26" t="n">
+      <c r="J26" t="n">
         <v>267.994122604021</v>
       </c>
-      <c r="E26" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="F26" t="n">
-        <v>28.01</v>
-      </c>
-      <c r="G26" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="H26" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>5.28</v>
-      </c>
       <c r="K26" t="n">
+        <v>245.531405903666</v>
+      </c>
+      <c r="L26" t="n">
         <v>41.4794454923274</v>
-      </c>
-      <c r="L26" t="n">
-        <v>245.531405903666</v>
       </c>
     </row>
     <row r="27">
@@ -79932,34 +80076,34 @@
         <v>15</v>
       </c>
       <c r="C27" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="D27" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I27" t="n">
         <v>10.2395260909091</v>
       </c>
-      <c r="D27" t="n">
+      <c r="J27" t="n">
         <v>3.73568969806763</v>
       </c>
-      <c r="E27" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="F27" t="n">
-        <v>16.45</v>
-      </c>
-      <c r="G27" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="H27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="I27" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.3</v>
-      </c>
       <c r="K27" t="n">
+        <v>4.09517245278876</v>
+      </c>
+      <c r="L27" t="n">
         <v>10.2057161868687</v>
-      </c>
-      <c r="L27" t="n">
-        <v>4.09517245278876</v>
       </c>
     </row>
     <row r="28">
@@ -79970,34 +80114,34 @@
         <v>15</v>
       </c>
       <c r="C28" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="D28" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8.14</v>
+      </c>
+      <c r="F28" t="n">
+        <v>34.06</v>
+      </c>
+      <c r="G28" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="H28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I28" t="n">
         <v>17.6603145698925</v>
       </c>
-      <c r="D28" t="n">
+      <c r="J28" t="n">
         <v>7.55113155913978</v>
       </c>
-      <c r="E28" t="n">
-        <v>80.25</v>
-      </c>
-      <c r="F28" t="n">
-        <v>34.27</v>
-      </c>
-      <c r="G28" t="n">
-        <v>8.14</v>
-      </c>
-      <c r="H28" t="n">
-        <v>34.06</v>
-      </c>
-      <c r="I28" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="J28" t="n">
-        <v>11.5</v>
-      </c>
       <c r="K28" t="n">
+        <v>10.5913258333333</v>
+      </c>
+      <c r="L28" t="n">
         <v>17.7723456372549</v>
-      </c>
-      <c r="L28" t="n">
-        <v>10.5913258333333</v>
       </c>
     </row>
     <row r="29">
@@ -80008,34 +80152,34 @@
         <v>15</v>
       </c>
       <c r="C29" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="I29" t="n">
         <v>4.18589166666667</v>
       </c>
-      <c r="D29" t="n">
+      <c r="J29" t="n">
         <v>3.1486621084619</v>
       </c>
-      <c r="E29" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="F29" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="G29" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="I29" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="J29" t="n">
-        <v>5.23</v>
-      </c>
       <c r="K29" t="n">
+        <v>3.24378015771526</v>
+      </c>
+      <c r="L29" t="n">
         <v>4.00612416666667</v>
-      </c>
-      <c r="L29" t="n">
-        <v>3.24378015771526</v>
       </c>
     </row>
     <row r="30">
@@ -80046,34 +80190,34 @@
         <v>15</v>
       </c>
       <c r="C30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="I30" t="n">
         <v>6.35389440993789</v>
       </c>
-      <c r="D30" t="n">
+      <c r="J30" t="n">
         <v>4.49451669254659</v>
       </c>
-      <c r="E30" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.49</v>
-      </c>
       <c r="K30" t="n">
+        <v>4.2931118513324</v>
+      </c>
+      <c r="L30" t="n">
         <v>6.04867882187939</v>
-      </c>
-      <c r="L30" t="n">
-        <v>4.2931118513324</v>
       </c>
     </row>
     <row r="31">
@@ -80084,34 +80228,34 @@
         <v>15</v>
       </c>
       <c r="C31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D31" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I31" t="n">
         <v>16.2561584799609</v>
       </c>
-      <c r="D31" t="n">
+      <c r="J31" t="n">
         <v>7.34821501657529</v>
       </c>
-      <c r="E31" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="F31" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="G31" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="H31" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="I31" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1.78</v>
-      </c>
       <c r="K31" t="n">
+        <v>7.02866663275982</v>
+      </c>
+      <c r="L31" t="n">
         <v>15.3026739081996</v>
-      </c>
-      <c r="L31" t="n">
-        <v>7.02866663275982</v>
       </c>
     </row>
     <row r="32">
@@ -80122,34 +80266,34 @@
         <v>15</v>
       </c>
       <c r="C32" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="D32" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="E32" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="F32" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="G32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I32" t="n">
         <v>43.793935</v>
       </c>
-      <c r="D32" t="n">
+      <c r="J32" t="n">
         <v>68.5325258695652</v>
       </c>
-      <c r="E32" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="F32" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="G32" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="H32" t="n">
-        <v>15.32</v>
-      </c>
-      <c r="I32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.41</v>
-      </c>
       <c r="K32" t="n">
+        <v>62.9977507905138</v>
+      </c>
+      <c r="L32" t="n">
         <v>40.8820621212121</v>
-      </c>
-      <c r="L32" t="n">
-        <v>62.9977507905138</v>
       </c>
     </row>
     <row r="33">
@@ -80160,34 +80304,102 @@
         <v>15</v>
       </c>
       <c r="C33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8.14</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="I33" t="n">
         <v>394.296229721833</v>
       </c>
-      <c r="D33" t="n">
+      <c r="J33" t="n">
         <v>25.878039913511</v>
       </c>
-      <c r="E33" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="F33" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="G33" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="H33" t="n">
-        <v>8.14</v>
-      </c>
-      <c r="I33" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="J33" t="n">
-        <v>5.47</v>
-      </c>
       <c r="K33" t="n">
+        <v>24.0526246270247</v>
+      </c>
+      <c r="L33" t="n">
         <v>360.200091805201</v>
       </c>
-      <c r="L33" t="n">
-        <v>24.0526246270247</v>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8.13</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34" t="n">
+        <v>2.92666666666667</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="F35" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35" t="n">
+        <v>2.85333333333333</v>
+      </c>
+      <c r="L35" t="n">
+        <v>6.78333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -80238,7 +80450,7 @@
         <v>45237</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" t="e">
         <v>#NUM!</v>
@@ -80261,7 +80473,7 @@
         <v>45237</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
         <v>23.414</v>
@@ -80290,7 +80502,7 @@
         <v>45237</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
         <v>10.054</v>
@@ -80319,7 +80531,7 @@
         <v>45237</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>84.052</v>
@@ -80348,7 +80560,7 @@
         <v>45237</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
         <v>90.222</v>
@@ -80377,7 +80589,7 @@
         <v>45237</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
         <v>21.702</v>
@@ -80406,7 +80618,7 @@
         <v>45265</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
         <v>72.8725</v>
@@ -80435,7 +80647,7 @@
         <v>45265</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
         <v>7.4375</v>
@@ -80464,7 +80676,7 @@
         <v>45265</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
         <v>13.915</v>
@@ -80493,7 +80705,7 @@
         <v>45265</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
         <v>69.755</v>
@@ -80522,7 +80734,7 @@
         <v>45265</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
         <v>151.2125</v>
@@ -80551,7 +80763,7 @@
         <v>45265</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
         <v>30.2625</v>
@@ -80580,7 +80792,7 @@
         <v>45294</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D14" t="e">
         <v>#NUM!</v>
@@ -80603,7 +80815,7 @@
         <v>45294</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
         <v>1.95034482758621</v>
@@ -80632,7 +80844,7 @@
         <v>45294</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
         <v>10.0188505747126</v>
@@ -80661,7 +80873,7 @@
         <v>45294</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
         <v>10.3044827586207</v>
@@ -80690,7 +80902,7 @@
         <v>45294</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D18" t="e">
         <v>#NUM!</v>
@@ -80713,7 +80925,7 @@
         <v>45294</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
         <v>29.7572413793103</v>
@@ -80742,7 +80954,7 @@
         <v>45334</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D20" t="n">
         <v>900.7705</v>
@@ -80771,7 +80983,7 @@
         <v>45334</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D21" t="n">
         <v>16.94875</v>
@@ -80800,7 +81012,7 @@
         <v>45334</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
         <v>10.353</v>
@@ -80829,7 +81041,7 @@
         <v>45334</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
         <v>38.75025</v>
@@ -80858,7 +81070,7 @@
         <v>45334</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
         <v>16.9586666666667</v>
@@ -80887,7 +81099,7 @@
         <v>45334</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D25" t="n">
         <v>9.16066666666667</v>
@@ -80916,7 +81128,7 @@
         <v>45356</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D26" t="n">
         <v>147.082727272727</v>
@@ -80945,7 +81157,7 @@
         <v>45356</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D27" t="n">
         <v>16.1795454545455</v>
@@ -80974,7 +81186,7 @@
         <v>45356</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D28" t="n">
         <v>21.0190909090909</v>
@@ -81003,7 +81215,7 @@
         <v>45356</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D29" t="n">
         <v>9.20818181818182</v>
@@ -81032,7 +81244,7 @@
         <v>45356</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
         <v>23.6090909090909</v>
@@ -81061,7 +81273,7 @@
         <v>45356</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D31" t="n">
         <v>9.63136363636364</v>
@@ -81090,7 +81302,7 @@
         <v>45391</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D32" t="n">
         <v>283.468</v>
@@ -81119,7 +81331,7 @@
         <v>45391</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D33" t="n">
         <v>6.7</v>
@@ -81148,7 +81360,7 @@
         <v>45391</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D34" t="e">
         <v>#NUM!</v>
@@ -81171,7 +81383,7 @@
         <v>45391</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D35" t="n">
         <v>41.054</v>
@@ -81200,7 +81412,7 @@
         <v>45391</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D36" t="e">
         <v>#NUM!</v>
@@ -81223,7 +81435,7 @@
         <v>45391</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D37" t="n">
         <v>15.502</v>
@@ -81252,7 +81464,7 @@
         <v>45418</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D38" t="n">
         <v>126.534074074074</v>
@@ -81281,7 +81493,7 @@
         <v>45418</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D39" t="n">
         <v>19.4833333333333</v>
@@ -81310,7 +81522,7 @@
         <v>45418</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D40" t="n">
         <v>6.17555555555556</v>
@@ -81339,7 +81551,7 @@
         <v>45418</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D41" t="n">
         <v>38.9718518518518</v>
@@ -81368,7 +81580,7 @@
         <v>45418</v>
       </c>
       <c r="C42" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D42" t="n">
         <v>29.2911111111111</v>
@@ -81397,7 +81609,7 @@
         <v>45418</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D43" t="n">
         <v>24.5985185185185</v>
@@ -81426,7 +81638,7 @@
         <v>45446</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D44" t="n">
         <v>54.0625</v>
@@ -81455,7 +81667,7 @@
         <v>45446</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D45" t="n">
         <v>28.89</v>
@@ -81484,7 +81696,7 @@
         <v>45446</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D46" t="n">
         <v>10.765</v>
@@ -81513,7 +81725,7 @@
         <v>45446</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D47" t="n">
         <v>20.58</v>
@@ -81542,7 +81754,7 @@
         <v>45446</v>
       </c>
       <c r="C48" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D48" t="n">
         <v>14.0875</v>
@@ -81571,7 +81783,7 @@
         <v>45446</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D49" t="n">
         <v>15.2175</v>
@@ -81600,7 +81812,7 @@
         <v>45482</v>
       </c>
       <c r="C50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D50" t="n">
         <v>43.3974074074074</v>
@@ -81629,7 +81841,7 @@
         <v>45482</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D51" t="n">
         <v>19.1916666666667</v>
@@ -81658,7 +81870,7 @@
         <v>45482</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D52" t="n">
         <v>11.2622222222222</v>
@@ -81687,7 +81899,7 @@
         <v>45482</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D53" t="n">
         <v>19.3025</v>
@@ -81716,7 +81928,7 @@
         <v>45482</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D54" t="n">
         <v>20.7725</v>
@@ -81745,7 +81957,7 @@
         <v>45482</v>
       </c>
       <c r="C55" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D55" t="n">
         <v>8.63722222222222</v>
@@ -81774,7 +81986,7 @@
         <v>45510</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D56" t="n">
         <v>16.9125</v>
@@ -81803,7 +82015,7 @@
         <v>45510</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D57" t="n">
         <v>16.2875</v>
@@ -81832,7 +82044,7 @@
         <v>45510</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D58" t="n">
         <v>9.43333333333333</v>
@@ -81861,7 +82073,7 @@
         <v>45510</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D59" t="n">
         <v>37.46</v>
@@ -81890,7 +82102,7 @@
         <v>45510</v>
       </c>
       <c r="C60" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D60" t="e">
         <v>#NUM!</v>
@@ -81913,7 +82125,7 @@
         <v>45510</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D61" t="n">
         <v>31.335</v>
@@ -81942,7 +82154,7 @@
         <v>45538</v>
       </c>
       <c r="C62" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D62" t="n">
         <v>14.4975</v>
@@ -81971,7 +82183,7 @@
         <v>45538</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D63" t="n">
         <v>15.2875</v>
@@ -82000,7 +82212,7 @@
         <v>45538</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D64" t="e">
         <v>#NUM!</v>
@@ -82023,7 +82235,7 @@
         <v>45538</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D65" t="n">
         <v>8.3</v>
@@ -82052,7 +82264,7 @@
         <v>45538</v>
       </c>
       <c r="C66" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D66" t="n">
         <v>8.7325</v>
@@ -82081,7 +82293,7 @@
         <v>45538</v>
       </c>
       <c r="C67" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D67" t="n">
         <v>22.05</v>
@@ -82110,7 +82322,7 @@
         <v>45567</v>
       </c>
       <c r="C68" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D68" t="n">
         <v>66.9996551724138</v>
@@ -82139,7 +82351,7 @@
         <v>45567</v>
       </c>
       <c r="C69" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D69" t="n">
         <v>16.5996551724138</v>
@@ -82168,7 +82380,7 @@
         <v>45567</v>
       </c>
       <c r="C70" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D70" t="n">
         <v>11.9241379310345</v>
@@ -82197,7 +82409,7 @@
         <v>45567</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D71" t="n">
         <v>33.4455172413793</v>
@@ -82226,7 +82438,7 @@
         <v>45567</v>
       </c>
       <c r="C72" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D72" t="n">
         <v>25.5258620689655</v>
@@ -82255,7 +82467,7 @@
         <v>45567</v>
       </c>
       <c r="C73" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D73" t="n">
         <v>35.9896551724138</v>
@@ -82284,7 +82496,7 @@
         <v>45601</v>
       </c>
       <c r="C74" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D74" t="n">
         <v>62.4729411764706</v>
@@ -82313,7 +82525,7 @@
         <v>45601</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D75" t="n">
         <v>7.80705882352941</v>
@@ -82342,7 +82554,7 @@
         <v>45601</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D76" t="n">
         <v>11.4923529411765</v>
@@ -82371,7 +82583,7 @@
         <v>45601</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D77" t="n">
         <v>23.9688235294118</v>
@@ -82400,7 +82612,7 @@
         <v>45601</v>
       </c>
       <c r="C78" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D78" t="n">
         <v>27.0323529411765</v>
@@ -82429,7 +82641,7 @@
         <v>45601</v>
       </c>
       <c r="C79" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D79" t="n">
         <v>31.2858823529412</v>
@@ -82458,7 +82670,7 @@
         <v>45630</v>
       </c>
       <c r="C80" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D80" t="e">
         <v>#NUM!</v>
@@ -82481,7 +82693,7 @@
         <v>45630</v>
       </c>
       <c r="C81" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D81" t="n">
         <v>7.5551724137931</v>
@@ -82510,7 +82722,7 @@
         <v>45630</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D82" t="n">
         <v>2.74206896551724</v>
@@ -82533,7 +82745,7 @@
         <v>45630</v>
       </c>
       <c r="C83" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D83" t="n">
         <v>11.8613793103448</v>
@@ -82562,7 +82774,7 @@
         <v>45630</v>
       </c>
       <c r="C84" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D84" t="n">
         <v>29.89</v>
@@ -82591,7 +82803,7 @@
         <v>45630</v>
       </c>
       <c r="C85" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D85" t="n">
         <v>21.188275862069</v>
@@ -82620,7 +82832,7 @@
         <v>45663</v>
       </c>
       <c r="C86" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D86" t="n">
         <v>101.875454545455</v>
@@ -82649,7 +82861,7 @@
         <v>45663</v>
       </c>
       <c r="C87" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D87" t="n">
         <v>7.9969696969697</v>
@@ -82678,7 +82890,7 @@
         <v>45663</v>
       </c>
       <c r="C88" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D88" t="n">
         <v>18.4545454545455</v>
@@ -82707,7 +82919,7 @@
         <v>45663</v>
       </c>
       <c r="C89" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D89" t="n">
         <v>26.8206060606061</v>
@@ -82736,7 +82948,7 @@
         <v>45663</v>
       </c>
       <c r="C90" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D90" t="n">
         <v>16.0660606060606</v>
@@ -82765,7 +82977,7 @@
         <v>45663</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D91" t="n">
         <v>15.6481818181818</v>
@@ -82794,7 +83006,7 @@
         <v>45699</v>
       </c>
       <c r="C92" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D92" t="n">
         <v>86.6833333333333</v>
@@ -82823,7 +83035,7 @@
         <v>45699</v>
       </c>
       <c r="C93" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D93" t="n">
         <v>8.9237037037037</v>
@@ -82852,7 +83064,7 @@
         <v>45699</v>
       </c>
       <c r="C94" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D94" t="n">
         <v>7.99555555555555</v>
@@ -82881,7 +83093,7 @@
         <v>45699</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D95" t="n">
         <v>7.72138888888889</v>
@@ -82910,7 +83122,7 @@
         <v>45699</v>
       </c>
       <c r="C96" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D96" t="n">
         <v>14.6222222222222</v>
@@ -82939,7 +83151,7 @@
         <v>45699</v>
       </c>
       <c r="C97" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D97" t="n">
         <v>11.2738888888889</v>
@@ -82968,7 +83180,7 @@
         <v>45733</v>
       </c>
       <c r="C98" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D98" t="n">
         <v>75.7564705882353</v>
@@ -82997,7 +83209,7 @@
         <v>45733</v>
       </c>
       <c r="C99" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D99" t="n">
         <v>5.57117647058824</v>
@@ -83026,7 +83238,7 @@
         <v>45733</v>
       </c>
       <c r="C100" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D100" t="n">
         <v>9.8</v>
@@ -83049,7 +83261,7 @@
         <v>45733</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D101" t="n">
         <v>25.6426470588235</v>
@@ -83078,7 +83290,7 @@
         <v>45733</v>
       </c>
       <c r="C102" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D102" t="n">
         <v>13.0652941176471</v>
@@ -83107,7 +83319,7 @@
         <v>45733</v>
       </c>
       <c r="C103" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D103" t="n">
         <v>19.1388235294118</v>
@@ -83136,7 +83348,7 @@
         <v>45755</v>
       </c>
       <c r="C104" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D104" t="n">
         <v>27.1981818181818</v>
@@ -83165,7 +83377,7 @@
         <v>45755</v>
       </c>
       <c r="C105" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D105" t="n">
         <v>13.37</v>
@@ -83194,7 +83406,7 @@
         <v>45755</v>
       </c>
       <c r="C106" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D106" t="n">
         <v>8.34272727272727</v>
@@ -83223,7 +83435,7 @@
         <v>45755</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D107" t="n">
         <v>14.9418181818182</v>
@@ -83252,7 +83464,7 @@
         <v>45755</v>
       </c>
       <c r="C108" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D108" t="n">
         <v>10.0333333333333</v>
@@ -83281,7 +83493,7 @@
         <v>45755</v>
       </c>
       <c r="C109" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D109" t="n">
         <v>11.9890909090909</v>
@@ -83310,7 +83522,7 @@
         <v>45783</v>
       </c>
       <c r="C110" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D110" t="e">
         <v>#NUM!</v>
@@ -83333,7 +83545,7 @@
         <v>45783</v>
       </c>
       <c r="C111" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D111" t="e">
         <v>#NUM!</v>
@@ -83356,7 +83568,7 @@
         <v>45783</v>
       </c>
       <c r="C112" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D112" t="e">
         <v>#NUM!</v>
@@ -83379,7 +83591,7 @@
         <v>45783</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D113" t="e">
         <v>#NUM!</v>
@@ -83402,7 +83614,7 @@
         <v>45783</v>
       </c>
       <c r="C114" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D114" t="e">
         <v>#NUM!</v>
@@ -83425,7 +83637,7 @@
         <v>45783</v>
       </c>
       <c r="C115" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D115" t="e">
         <v>#NUM!</v>
@@ -83448,7 +83660,7 @@
         <v>45818</v>
       </c>
       <c r="C116" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D116" t="n">
         <v>9.164</v>
@@ -83477,7 +83689,7 @@
         <v>45818</v>
       </c>
       <c r="C117" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D117" t="n">
         <v>7.462</v>
@@ -83506,7 +83718,7 @@
         <v>45818</v>
       </c>
       <c r="C118" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D118" t="n">
         <v>8.336</v>
@@ -83535,7 +83747,7 @@
         <v>45818</v>
       </c>
       <c r="C119" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D119" t="n">
         <v>23.078</v>
@@ -83564,7 +83776,7 @@
         <v>45818</v>
       </c>
       <c r="C120" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D120" t="n">
         <v>14.77</v>
@@ -83593,7 +83805,7 @@
         <v>45818</v>
       </c>
       <c r="C121" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D121" t="n">
         <v>12.826</v>
@@ -83622,7 +83834,7 @@
         <v>45846</v>
       </c>
       <c r="C122" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D122" t="n">
         <v>25.645</v>
@@ -83651,7 +83863,7 @@
         <v>45846</v>
       </c>
       <c r="C123" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D123" t="n">
         <v>5.815</v>
@@ -83680,7 +83892,7 @@
         <v>45846</v>
       </c>
       <c r="C124" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D124" t="n">
         <v>11.305</v>
@@ -83709,7 +83921,7 @@
         <v>45846</v>
       </c>
       <c r="C125" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D125" t="n">
         <v>16.49</v>
@@ -83738,7 +83950,7 @@
         <v>45846</v>
       </c>
       <c r="C126" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D126" t="n">
         <v>13.2525</v>
@@ -83767,7 +83979,7 @@
         <v>45846</v>
       </c>
       <c r="C127" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D127" t="n">
         <v>10.4675</v>
@@ -83796,7 +84008,7 @@
         <v>45874</v>
       </c>
       <c r="C128" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D128" t="n">
         <v>25.815</v>
@@ -83825,7 +84037,7 @@
         <v>45874</v>
       </c>
       <c r="C129" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D129" t="n">
         <v>20.985</v>
@@ -83854,7 +84066,7 @@
         <v>45874</v>
       </c>
       <c r="C130" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D130" t="n">
         <v>11.4325</v>
@@ -83883,7 +84095,7 @@
         <v>45874</v>
       </c>
       <c r="C131" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D131" t="n">
         <v>22.4175</v>
@@ -83912,7 +84124,7 @@
         <v>45874</v>
       </c>
       <c r="C132" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D132" t="n">
         <v>13.7766666666667</v>
@@ -83941,7 +84153,7 @@
         <v>45874</v>
       </c>
       <c r="C133" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D133" t="n">
         <v>11.76</v>
@@ -83970,7 +84182,7 @@
         <v>45902</v>
       </c>
       <c r="C134" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D134" t="n">
         <v>25.52</v>
@@ -83999,7 +84211,7 @@
         <v>45902</v>
       </c>
       <c r="C135" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D135" t="n">
         <v>8.495</v>
@@ -84028,7 +84240,7 @@
         <v>45902</v>
       </c>
       <c r="C136" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D136" t="n">
         <v>8.33333333333333</v>
@@ -84057,7 +84269,7 @@
         <v>45902</v>
       </c>
       <c r="C137" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D137" t="n">
         <v>40.4425</v>
@@ -84086,7 +84298,7 @@
         <v>45902</v>
       </c>
       <c r="C138" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D138" t="n">
         <v>22.915</v>
@@ -84115,7 +84327,7 @@
         <v>45902</v>
       </c>
       <c r="C139" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D139" t="n">
         <v>15.995</v>
@@ -84144,7 +84356,7 @@
         <v>45937</v>
       </c>
       <c r="C140" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D140" t="n">
         <v>26.15</v>
@@ -84173,7 +84385,7 @@
         <v>45937</v>
       </c>
       <c r="C141" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D141" t="n">
         <v>10.114</v>
@@ -84202,7 +84414,7 @@
         <v>45937</v>
       </c>
       <c r="C142" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D142" t="n">
         <v>11.092</v>
@@ -84231,7 +84443,7 @@
         <v>45937</v>
       </c>
       <c r="C143" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D143" t="n">
         <v>51.668</v>
@@ -84260,7 +84472,7 @@
         <v>45937</v>
       </c>
       <c r="C144" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D144" t="n">
         <v>29.178</v>
@@ -84289,7 +84501,7 @@
         <v>45937</v>
       </c>
       <c r="C145" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D145" t="n">
         <v>14.222</v>
@@ -84318,7 +84530,7 @@
         <v>45965</v>
       </c>
       <c r="C146" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D146" t="n">
         <v>17.265</v>
@@ -84347,7 +84559,7 @@
         <v>45965</v>
       </c>
       <c r="C147" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D147" t="n">
         <v>29.04</v>
@@ -84376,7 +84588,7 @@
         <v>45965</v>
       </c>
       <c r="C148" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D148" t="n">
         <v>25.7875</v>
@@ -84405,7 +84617,7 @@
         <v>45965</v>
       </c>
       <c r="C149" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D149" t="n">
         <v>25.6975</v>
@@ -84434,7 +84646,7 @@
         <v>45965</v>
       </c>
       <c r="C150" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D150" t="n">
         <v>38.475</v>
@@ -84463,7 +84675,7 @@
         <v>45965</v>
       </c>
       <c r="C151" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D151" t="n">
         <v>29.6825</v>
@@ -84492,7 +84704,7 @@
         <v>45993</v>
       </c>
       <c r="C152" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D152" t="n">
         <v>30.7375</v>
@@ -84521,7 +84733,7 @@
         <v>45993</v>
       </c>
       <c r="C153" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D153" t="n">
         <v>54.19</v>
@@ -84550,7 +84762,7 @@
         <v>45993</v>
       </c>
       <c r="C154" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D154" t="n">
         <v>22.9133333333333</v>
@@ -84579,7 +84791,7 @@
         <v>45993</v>
       </c>
       <c r="C155" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D155" t="n">
         <v>35.16</v>
@@ -84608,7 +84820,7 @@
         <v>45993</v>
       </c>
       <c r="C156" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D156" t="n">
         <v>25.7075</v>
@@ -84637,7 +84849,7 @@
         <v>45993</v>
       </c>
       <c r="C157" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D157" t="n">
         <v>11.0425</v>
@@ -84666,7 +84878,7 @@
         <v>46028</v>
       </c>
       <c r="C158" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D158" t="n">
         <v>71.198</v>
@@ -84695,7 +84907,7 @@
         <v>46028</v>
       </c>
       <c r="C159" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D159" t="n">
         <v>18.788</v>
@@ -84724,7 +84936,7 @@
         <v>46028</v>
       </c>
       <c r="C160" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D160" t="n">
         <v>15.03</v>
@@ -84753,7 +84965,7 @@
         <v>46028</v>
       </c>
       <c r="C161" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D161" t="n">
         <v>10.448</v>
@@ -84782,7 +84994,7 @@
         <v>46028</v>
       </c>
       <c r="C162" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D162" t="n">
         <v>19.164</v>
@@ -84811,7 +85023,7 @@
         <v>46028</v>
       </c>
       <c r="C163" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D163" t="n">
         <v>9.71</v>
@@ -84840,7 +85052,7 @@
         <v>46063</v>
       </c>
       <c r="C164" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D164" t="n">
         <v>50.136</v>
@@ -84869,7 +85081,7 @@
         <v>46063</v>
       </c>
       <c r="C165" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D165" t="n">
         <v>4.196</v>
@@ -84898,7 +85110,7 @@
         <v>46063</v>
       </c>
       <c r="C166" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D166" t="n">
         <v>8.688</v>
@@ -84927,7 +85139,7 @@
         <v>46063</v>
       </c>
       <c r="C167" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D167" t="n">
         <v>11.928</v>
@@ -84956,7 +85168,7 @@
         <v>46063</v>
       </c>
       <c r="C168" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D168" t="n">
         <v>18.386</v>
@@ -84985,7 +85197,7 @@
         <v>46063</v>
       </c>
       <c r="C169" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D169" t="n">
         <v>6.168</v>
@@ -85014,7 +85226,7 @@
         <v>46091</v>
       </c>
       <c r="C170" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D170" t="n">
         <v>54.51</v>
@@ -85043,7 +85255,7 @@
         <v>46091</v>
       </c>
       <c r="C171" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D171" t="n">
         <v>17.6975</v>
@@ -85072,7 +85284,7 @@
         <v>46091</v>
       </c>
       <c r="C172" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D172" t="e">
         <v>#NUM!</v>
@@ -85095,7 +85307,7 @@
         <v>46091</v>
       </c>
       <c r="C173" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D173" t="n">
         <v>11.97</v>
@@ -85124,7 +85336,7 @@
         <v>46091</v>
       </c>
       <c r="C174" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D174" t="n">
         <v>26.4775</v>
@@ -85153,7 +85365,7 @@
         <v>46091</v>
       </c>
       <c r="C175" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D175" t="n">
         <v>8.49</v>
@@ -85182,7 +85394,7 @@
         <v>46125</v>
       </c>
       <c r="C176" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D176" t="n">
         <v>170.291470588235</v>
@@ -85211,7 +85423,7 @@
         <v>46125</v>
       </c>
       <c r="C177" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D177" t="n">
         <v>6.84970588235294</v>
@@ -85240,7 +85452,7 @@
         <v>46125</v>
       </c>
       <c r="C178" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D178" t="n">
         <v>7.26147058823529</v>
@@ -85269,7 +85481,7 @@
         <v>46125</v>
       </c>
       <c r="C179" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D179" t="n">
         <v>20.4688235294118</v>
@@ -85298,7 +85510,7 @@
         <v>46125</v>
       </c>
       <c r="C180" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D180" t="n">
         <v>16.1432352941176</v>
@@ -85327,7 +85539,7 @@
         <v>46125</v>
       </c>
       <c r="C181" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D181" t="n">
         <v>9.64764705882353</v>
@@ -85356,7 +85568,7 @@
         <v>46147</v>
       </c>
       <c r="C182" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D182" t="n">
         <v>113.075454545455</v>
@@ -85385,7 +85597,7 @@
         <v>46147</v>
       </c>
       <c r="C183" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D183" t="n">
         <v>18.6740909090909</v>
@@ -85414,7 +85626,7 @@
         <v>46147</v>
       </c>
       <c r="C184" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D184" t="n">
         <v>10.2369696969697</v>
@@ -85443,7 +85655,7 @@
         <v>46147</v>
       </c>
       <c r="C185" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D185" t="n">
         <v>15.8327272727273</v>
@@ -85472,7 +85684,7 @@
         <v>46147</v>
       </c>
       <c r="C186" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D186" t="n">
         <v>20.8886363636364</v>
@@ -85501,7 +85713,7 @@
         <v>46147</v>
       </c>
       <c r="C187" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D187" t="n">
         <v>14.9386363636364</v>
@@ -85520,6 +85732,348 @@
       </c>
       <c r="I187" t="n">
         <v>0.439824266809974</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B188" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C188" t="s">
+        <v>20</v>
+      </c>
+      <c r="D188" t="n">
+        <v>48.6625</v>
+      </c>
+      <c r="E188" t="n">
+        <v>17.1522794889387</v>
+      </c>
+      <c r="F188" t="n">
+        <v>3.30371904187591</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1.40123714804336</v>
+      </c>
+      <c r="H188" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0.588374597230941</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B189" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C189" t="s">
+        <v>21</v>
+      </c>
+      <c r="D189" t="n">
+        <v>7.5775</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2.41675229733348</v>
+      </c>
+      <c r="F189" t="n">
+        <v>13.7825407910332</v>
+      </c>
+      <c r="G189" t="n">
+        <v>5.95640362438062</v>
+      </c>
+      <c r="H189" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.551233163008177</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B190" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C190" t="s">
+        <v>22</v>
+      </c>
+      <c r="D190" t="n">
+        <v>9.9425</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3.06765246836513</v>
+      </c>
+      <c r="F190" t="n">
+        <v>18.9605473983287</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1.18866462448694</v>
+      </c>
+      <c r="H190" t="n">
+        <v>1.90975</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.673201988014494</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B191" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C191" t="s">
+        <v>23</v>
+      </c>
+      <c r="D191" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="E191" t="n">
+        <v>4.86905192688132</v>
+      </c>
+      <c r="F191" t="n">
+        <v>17.0482024621369</v>
+      </c>
+      <c r="G191" t="n">
+        <v>3.37901615207695</v>
+      </c>
+      <c r="H191" t="n">
+        <v>4.6955</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.751847723944151</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B192" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C192" t="s">
+        <v>24</v>
+      </c>
+      <c r="D192" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E192" t="n">
+        <v>20.1261637344693</v>
+      </c>
+      <c r="F192" t="n">
+        <v>19.3235040301298</v>
+      </c>
+      <c r="G192" t="n">
+        <v>4.82554513722088</v>
+      </c>
+      <c r="H192" t="n">
+        <v>5.32625</v>
+      </c>
+      <c r="I192" t="n">
+        <v>4.97784902509775</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B193" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C193" t="s">
+        <v>25</v>
+      </c>
+      <c r="D193" t="n">
+        <v>9.70666666666667</v>
+      </c>
+      <c r="E193" t="n">
+        <v>4.76798000555092</v>
+      </c>
+      <c r="F193" t="n">
+        <v>15.1711201195307</v>
+      </c>
+      <c r="G193" t="n">
+        <v>7.77828434098742</v>
+      </c>
+      <c r="H193" t="n">
+        <v>1.701</v>
+      </c>
+      <c r="I193" t="n">
+        <v>1.56828791999429</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B194" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C194" t="s">
+        <v>20</v>
+      </c>
+      <c r="D194" t="n">
+        <v>20.2034482758621</v>
+      </c>
+      <c r="E194" t="n">
+        <v>2.72406791704003</v>
+      </c>
+      <c r="F194" t="n">
+        <v>6.42531868581686</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1.84293896144585</v>
+      </c>
+      <c r="H194" t="n">
+        <v>1.27303448275862</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0.197307174943507</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B195" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C195" t="s">
+        <v>21</v>
+      </c>
+      <c r="D195" t="n">
+        <v>32.711724137931</v>
+      </c>
+      <c r="E195" t="n">
+        <v>9.48986066337256</v>
+      </c>
+      <c r="F195" t="n">
+        <v>23.7078890955488</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0.0868301575419838</v>
+      </c>
+      <c r="H195" t="n">
+        <v>7.75937931034483</v>
+      </c>
+      <c r="I195" t="n">
+        <v>2.27824928299814</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B196" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C196" t="s">
+        <v>22</v>
+      </c>
+      <c r="D196" t="n">
+        <v>15.168275862069</v>
+      </c>
+      <c r="E196"/>
+      <c r="F196" t="n">
+        <v>17.7275620623806</v>
+      </c>
+      <c r="G196"/>
+      <c r="H196" t="n">
+        <v>2.68896551724138</v>
+      </c>
+      <c r="I196"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B197" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C197" t="s">
+        <v>23</v>
+      </c>
+      <c r="D197" t="n">
+        <v>15.6558620689655</v>
+      </c>
+      <c r="E197" t="n">
+        <v>5.0862922260522</v>
+      </c>
+      <c r="F197" t="n">
+        <v>12.7115152503146</v>
+      </c>
+      <c r="G197" t="n">
+        <v>4.96693831281184</v>
+      </c>
+      <c r="H197" t="n">
+        <v>2.11641379310345</v>
+      </c>
+      <c r="I197" t="n">
+        <v>1.42416182329462</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B198" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C198" t="s">
+        <v>24</v>
+      </c>
+      <c r="D198" t="n">
+        <v>27.3434482758621</v>
+      </c>
+      <c r="E198" t="n">
+        <v>4.55902069297274</v>
+      </c>
+      <c r="F198" t="n">
+        <v>16.7170022699063</v>
+      </c>
+      <c r="G198" t="n">
+        <v>6.52566721951156</v>
+      </c>
+      <c r="H198" t="n">
+        <v>4.7131724137931</v>
+      </c>
+      <c r="I198" t="n">
+        <v>2.28115778295957</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B199" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C199" t="s">
+        <v>25</v>
+      </c>
+      <c r="D199" t="n">
+        <v>17.0993103448276</v>
+      </c>
+      <c r="E199" t="n">
+        <v>4.03125128469225</v>
+      </c>
+      <c r="F199" t="n">
+        <v>15.6588625238051</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1.84259266542743</v>
+      </c>
+      <c r="H199" t="n">
+        <v>2.67931034482758</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0.696194172485389</v>
       </c>
     </row>
   </sheetData>
@@ -85570,7 +86124,7 @@
         <v>45237</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
         <v>22.558</v>
@@ -85599,7 +86153,7 @@
         <v>45237</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
         <v>61.4426666666667</v>
@@ -85628,7 +86182,7 @@
         <v>45265</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
         <v>36.8575</v>
@@ -85657,7 +86211,7 @@
         <v>45265</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
         <v>78.2941666666667</v>
@@ -85686,7 +86240,7 @@
         <v>45294</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
         <v>15.8537931034483</v>
@@ -85715,7 +86269,7 @@
         <v>45294</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
         <v>10.1820689655172</v>
@@ -85744,7 +86298,7 @@
         <v>45334</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
         <v>336.214454545455</v>
@@ -85773,7 +86327,7 @@
         <v>45334</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
         <v>22.4808181818182</v>
@@ -85802,7 +86356,7 @@
         <v>45356</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
         <v>39.7409090909091</v>
@@ -85831,7 +86385,7 @@
         <v>45356</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
         <v>17.3307272727273</v>
@@ -85860,7 +86414,7 @@
         <v>45391</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" t="n">
         <v>65.5744</v>
@@ -85889,7 +86443,7 @@
         <v>45391</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
         <v>41.054</v>
@@ -85918,7 +86472,7 @@
         <v>45418</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
         <v>42.9395555555556</v>
@@ -85947,7 +86501,7 @@
         <v>45418</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
         <v>24.8128395061728</v>
@@ -85976,7 +86530,7 @@
         <v>45446</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" t="n">
         <v>32.7233333333333</v>
@@ -86005,7 +86559,7 @@
         <v>45446</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>15.1441666666667</v>
@@ -86034,7 +86588,7 @@
         <v>45482</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
         <v>21.9552525252525</v>
@@ -86063,7 +86617,7 @@
         <v>45482</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
         <v>17.1124074074074</v>
@@ -86092,7 +86646,7 @@
         <v>45510</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>21.5116666666667</v>
@@ -86121,7 +86675,7 @@
         <v>45510</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" t="n">
         <v>20.644</v>
@@ -86150,7 +86704,7 @@
         <v>45538</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" t="n">
         <v>16.324</v>
@@ -86179,7 +86733,7 @@
         <v>45538</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23" t="n">
         <v>8.58833333333333</v>
@@ -86208,7 +86762,7 @@
         <v>45567</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" t="n">
         <v>39.8629885057471</v>
@@ -86237,7 +86791,7 @@
         <v>45567</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D25" t="n">
         <v>23.6318390804598</v>
@@ -86266,7 +86820,7 @@
         <v>45601</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" t="n">
         <v>33.8552941176471</v>
@@ -86295,7 +86849,7 @@
         <v>45601</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" t="n">
         <v>22.6989411764706</v>
@@ -86324,7 +86878,7 @@
         <v>45630</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" t="n">
         <v>14.371724137931</v>
@@ -86353,7 +86907,7 @@
         <v>45630</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" t="n">
         <v>18.8608429118774</v>
@@ -86382,7 +86936,7 @@
         <v>45663</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" t="n">
         <v>48.6088484848485</v>
@@ -86411,7 +86965,7 @@
         <v>45663</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D31" t="n">
         <v>20.8455757575758</v>
@@ -86440,7 +86994,7 @@
         <v>45699</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D32" t="n">
         <v>27.2481481481481</v>
@@ -86469,7 +87023,7 @@
         <v>45699</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D33" t="n">
         <v>9.51513888888889</v>
@@ -86498,7 +87052,7 @@
         <v>45733</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" t="n">
         <v>39.0723529411765</v>
@@ -86527,7 +87081,7 @@
         <v>45733</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D35" t="n">
         <v>18.2924183006536</v>
@@ -86556,7 +87110,7 @@
         <v>45755</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D36" t="n">
         <v>19.0555555555556</v>
@@ -86585,7 +87139,7 @@
         <v>45755</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D37" t="n">
         <v>11.4513636363636</v>
@@ -86614,7 +87168,7 @@
         <v>45783</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D38" t="e">
         <v>#NUM!</v>
@@ -86637,7 +87191,7 @@
         <v>45783</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D39" t="e">
         <v>#NUM!</v>
@@ -86660,7 +87214,7 @@
         <v>45818</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D40" t="n">
         <v>9.81733333333333</v>
@@ -86689,7 +87243,7 @@
         <v>45818</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D41" t="n">
         <v>15.3946666666667</v>
@@ -86718,7 +87272,7 @@
         <v>45846</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D42" t="n">
         <v>13.9758333333333</v>
@@ -86747,7 +87301,7 @@
         <v>45846</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D43" t="n">
         <v>13.6825</v>
@@ -86776,7 +87330,7 @@
         <v>45874</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D44" t="n">
         <v>21.072</v>
@@ -86805,7 +87359,7 @@
         <v>45874</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D45" t="n">
         <v>16.0663636363636</v>
@@ -86834,7 +87388,7 @@
         <v>45902</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D46" t="n">
         <v>16.67</v>
@@ -86863,7 +87417,7 @@
         <v>45902</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D47" t="n">
         <v>25.3118181818182</v>
@@ -86892,7 +87446,7 @@
         <v>45937</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D48" t="n">
         <v>16.8286666666667</v>
@@ -86921,7 +87475,7 @@
         <v>45937</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D49" t="n">
         <v>30.646</v>
@@ -86950,7 +87504,7 @@
         <v>45965</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D50" t="n">
         <v>26.942</v>
@@ -86979,7 +87533,7 @@
         <v>45965</v>
       </c>
       <c r="C51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D51" t="n">
         <v>29.9866666666667</v>
@@ -87008,7 +87562,7 @@
         <v>45993</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D52" t="n">
         <v>29.9718181818182</v>
@@ -87037,7 +87591,7 @@
         <v>45993</v>
       </c>
       <c r="C53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D53" t="n">
         <v>28.3827272727273</v>
@@ -87066,7 +87620,7 @@
         <v>46028</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D54" t="n">
         <v>36.1208</v>
@@ -87095,7 +87649,7 @@
         <v>46028</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D55" t="n">
         <v>15.2836363636364</v>
@@ -87124,7 +87678,7 @@
         <v>46063</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D56" t="n">
         <v>22.9664</v>
@@ -87153,7 +87707,7 @@
         <v>46063</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D57" t="n">
         <v>14.347</v>
@@ -87182,7 +87736,7 @@
         <v>46091</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D58" t="n">
         <v>26.8991666666667</v>
@@ -87211,7 +87765,7 @@
         <v>46091</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D59" t="n">
         <v>19.22375</v>
@@ -87240,7 +87794,7 @@
         <v>46125</v>
       </c>
       <c r="C60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D60" t="n">
         <v>62.2629411764706</v>
@@ -87269,7 +87823,7 @@
         <v>46125</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D61" t="n">
         <v>14.6245098039216</v>
@@ -87298,7 +87852,7 @@
         <v>46147</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D62" t="n">
         <v>48.8960606060606</v>
@@ -87327,7 +87881,7 @@
         <v>46147</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D63" t="n">
         <v>16.1451239669421</v>
@@ -87346,6 +87900,122 @@
       </c>
       <c r="I63" t="n">
         <v>2.12099726625379</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C64" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" t="n">
+        <v>23.0981818181818</v>
+      </c>
+      <c r="E64" t="n">
+        <v>22.4973179815647</v>
+      </c>
+      <c r="F64" t="n">
+        <v>10.3507636082026</v>
+      </c>
+      <c r="G64" t="n">
+        <v>7.40803132634946</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.38209090909091</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.878701138561396</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C65" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" t="n">
+        <v>20.6241666666667</v>
+      </c>
+      <c r="E65" t="n">
+        <v>13.5955998619429</v>
+      </c>
+      <c r="F65" t="n">
+        <v>18.4440846301985</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3.3070733566154</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3.97716666666667</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3.07235964494373</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C66" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" t="n">
+        <v>22.4468965517241</v>
+      </c>
+      <c r="E66" t="n">
+        <v>8.53004006506959</v>
+      </c>
+      <c r="F66" t="n">
+        <v>15.3204290191638</v>
+      </c>
+      <c r="G66" t="n">
+        <v>7.18195446257697</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3.72896551724138</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3.00154725907723</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C67" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" t="n">
+        <v>22.2648275862069</v>
+      </c>
+      <c r="E67" t="n">
+        <v>7.40621165950999</v>
+      </c>
+      <c r="F67" t="n">
+        <v>15.716943091805</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5.4548408056082</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3.68206896551724</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2.15177381758151</v>
       </c>
     </row>
   </sheetData>
